--- a/backtest_runs/20260410_193731/by_symbol/POL/POL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/POL/POL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1075.450000000003</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98924.55</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>102314.18</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>102314.18</v>
@@ -725,7 +725,7 @@
         <v>-94.20000000000357</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>102219.98</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>102219.98</v>
@@ -863,7 +863,7 @@
         <v>-317.140000000015</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>101902.84</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>101902.84</v>
@@ -1047,7 +1047,7 @@
         <v>-615.4399999999936</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>105540.53</v>
@@ -1185,7 +1185,7 @@
         <v>-1475.799999999997</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>104520.03</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>104520.03</v>
@@ -1277,7 +1277,7 @@
         <v>-1055.040000000004</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>103464.99</v>
@@ -1415,7 +1415,7 @@
         <v>-62.79999999999643</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>104796.35</v>
@@ -1507,7 +1507,7 @@
         <v>-606.0200000000021</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>106126.14</v>
@@ -1645,7 +1645,7 @@
         <v>-1073.880000000005</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>109393.31</v>
